--- a/config/anomaly-arbitration-generated/templates/AnomalyArbitrationBindings.xlsx
+++ b/config/anomaly-arbitration-generated/templates/AnomalyArbitrationBindings.xlsx
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="92">
   <si>
     <t>@table</t>
   </si>
   <si>
-    <t>AAPoolAudits</t>
+    <t>ArbPoolAudits</t>
   </si>
   <si>
     <t>@mode</t>
@@ -54,7 +54,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>ed127f6c3cfca95f</t>
+    <t>ea96522519939b13</t>
   </si>
   <si>
     <t>#name</t>
@@ -117,16 +117,19 @@
     <t>string</t>
   </si>
   <si>
-    <t>enum&lt;AAOwnership&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;AACoverageState&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;AAEvidenceQuality&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;AAMechanismQuality&gt;</t>
+    <t>enum&lt;ArbOwnership&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;ArbCoverageState&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;ArbEvidenceQuality&gt;</t>
+  </si>
+  <si>
+    <t>enum&lt;ArbMechanismQuality&gt;</t>
+  </si>
+  <si>
+    <t>optional&lt;list&lt;string&gt;&gt;</t>
   </si>
   <si>
     <t>list&lt;string&gt;</t>
@@ -168,10 +171,10 @@
     <t>#desc</t>
   </si>
   <si>
-    <t>AATraits</t>
-  </si>
-  <si>
-    <t>1f7f8871d00f8efe</t>
+    <t>ArbTraits</t>
+  </si>
+  <si>
+    <t>ca3c4d009c8be015</t>
   </si>
   <si>
     <t>source_numeric_id</t>
@@ -180,10 +183,10 @@
     <t>length=1..64</t>
   </si>
   <si>
-    <t>AAMazeBuffBindings</t>
-  </si>
-  <si>
-    <t>bb8a9f152994121e</t>
+    <t>ArbMazeBuffBindings</t>
+  </si>
+  <si>
+    <t>337d8302b80437df</t>
   </si>
   <si>
     <t>stage_stable_key</t>
@@ -198,16 +201,16 @@
     <t>range=1..1000</t>
   </si>
   <si>
-    <t>AABattleEvents</t>
-  </si>
-  <si>
-    <t>50a1bfd3083c25c4</t>
-  </si>
-  <si>
-    <t>AAEncounters</t>
-  </si>
-  <si>
-    <t>ee2ae0cb45ce5293</t>
+    <t>ArbBattleEvents</t>
+  </si>
+  <si>
+    <t>4ceb66e71fca8713</t>
+  </si>
+  <si>
+    <t>ArbEncounters</t>
+  </si>
+  <si>
+    <t>668e047fec4b6deb</t>
   </si>
   <si>
     <t>stage_id</t>
@@ -216,13 +219,13 @@
     <t>source_stage_id</t>
   </si>
   <si>
-    <t>ref&lt;AAStages.id&gt;</t>
-  </si>
-  <si>
-    <t>AAEncounterWaves</t>
-  </si>
-  <si>
-    <t>16a5cf2f2226feef</t>
+    <t>ref&lt;ArbStages.id&gt;</t>
+  </si>
+  <si>
+    <t>ArbEncounterWaves</t>
+  </si>
+  <si>
+    <t>31223a9c656975a7</t>
   </si>
   <si>
     <t>encounter_id</t>
@@ -231,16 +234,16 @@
     <t>wave_order</t>
   </si>
   <si>
-    <t>ref&lt;AAEncounters.id&gt;</t>
+    <t>ref&lt;ArbEncounters.id&gt;</t>
   </si>
   <si>
     <t>range=1..100</t>
   </si>
   <si>
-    <t>AAEnemySlots</t>
-  </si>
-  <si>
-    <t>6096a90a2a184f0c</t>
+    <t>ArbEnemySlots</t>
+  </si>
+  <si>
+    <t>02dd37249b6b153b</t>
   </si>
   <si>
     <t>slot_order</t>
@@ -249,46 +252,46 @@
     <t>enemy_id</t>
   </si>
   <si>
-    <t>ref&lt;AAEnemies.id&gt;</t>
-  </si>
-  <si>
-    <t>AAEnemies</t>
-  </si>
-  <si>
-    <t>a504f5d7415d81d4</t>
+    <t>ref&lt;ArbEnemies.id&gt;</t>
+  </si>
+  <si>
+    <t>ArbEnemies</t>
+  </si>
+  <si>
+    <t>c9a15a3f6a4e39b7</t>
   </si>
   <si>
     <t>source_template_id</t>
   </si>
   <si>
-    <t>AAEnemySkills</t>
-  </si>
-  <si>
-    <t>907f438c9147c79f</t>
+    <t>ArbEnemySkills</t>
+  </si>
+  <si>
+    <t>8c8ee4564c307d0d</t>
   </si>
   <si>
     <t>skill_order</t>
   </si>
   <si>
-    <t>AAEnemyStatuses</t>
-  </si>
-  <si>
-    <t>e5f289b38b3df0d3</t>
+    <t>ArbEnemyStatuses</t>
+  </si>
+  <si>
+    <t>0c1fd8aafc075210</t>
   </si>
   <si>
     <t>owner_stable_key</t>
   </si>
   <si>
-    <t>AAAbilityBindings</t>
-  </si>
-  <si>
-    <t>e60b8006b177da8d</t>
-  </si>
-  <si>
-    <t>AAMechanicContributions</t>
-  </si>
-  <si>
-    <t>688223c3b7fd16fd</t>
+    <t>ArbAbilityBindings</t>
+  </si>
+  <si>
+    <t>2f23232bff31f82a</t>
+  </si>
+  <si>
+    <t>ArbMechanicContributions</t>
+  </si>
+  <si>
+    <t>2cafbb916b7eb9ca</t>
   </si>
   <si>
     <t>scope</t>
@@ -720,11 +723,11 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
+    <col min="13" max="13" width="22.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" style="5" customWidth="1"/>
@@ -910,13 +913,13 @@
         <v>34</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>29</v>
@@ -924,7 +927,7 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -977,50 +980,50 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1049,16 +1052,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -1077,10 +1080,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -1094,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1118,7 +1121,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -1171,10 +1174,10 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1227,10 +1230,10 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1271,16 +1274,16 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>29</v>
@@ -1291,7 +1294,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -1347,53 +1350,53 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1423,16 +1426,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -1451,10 +1454,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -1468,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1492,7 +1495,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -1545,10 +1548,10 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1601,10 +1604,10 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1645,16 +1648,16 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>29</v>
@@ -1665,7 +1668,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -1721,53 +1724,53 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1797,16 +1800,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -1829,10 +1832,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -1846,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1870,7 +1873,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -1923,10 +1926,10 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1979,10 +1982,10 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2023,16 +2026,16 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>29</v>
@@ -2043,7 +2046,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -2099,53 +2102,53 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2175,16 +2178,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -2207,10 +2210,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -2223,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2247,7 +2250,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -2300,7 +2303,7 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -2353,7 +2356,7 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -2394,16 +2397,16 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>29</v>
@@ -2411,7 +2414,7 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -2464,50 +2467,50 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2536,16 +2539,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -2564,10 +2567,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -2581,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2605,7 +2608,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -2658,10 +2661,10 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2714,10 +2717,10 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2758,16 +2761,16 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>29</v>
@@ -2778,7 +2781,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -2834,53 +2837,53 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2910,16 +2913,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -2942,10 +2945,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -2958,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2982,7 +2985,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -3035,7 +3038,7 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -3088,7 +3091,7 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -3129,16 +3132,16 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>29</v>
@@ -3146,7 +3149,7 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -3199,50 +3202,50 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3271,16 +3274,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -3299,15 +3302,15 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" style="5" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="17.7109375" style="5" customWidth="1"/>
     <col min="18" max="18" width="15.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3316,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3340,7 +3343,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -3393,10 +3396,10 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -3449,10 +3452,10 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -3493,19 +3496,19 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>29</v>
@@ -3513,7 +3516,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -3569,51 +3572,51 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3643,16 +3646,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -3671,15 +3674,15 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" style="5" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="21.7109375" style="5" customWidth="1"/>
     <col min="18" max="18" width="12.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3688,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3712,7 +3715,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -3765,10 +3768,10 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -3821,10 +3824,10 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -3865,19 +3868,19 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>28</v>
@@ -3885,7 +3888,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -3941,51 +3944,51 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4015,16 +4018,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -4047,17 +4050,17 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" style="5" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" style="5" customWidth="1"/>
+    <col min="17" max="17" width="21.7109375" style="5" customWidth="1"/>
     <col min="18" max="19" width="12.7109375" style="5" customWidth="1"/>
-    <col min="20" max="20" width="17.7109375" style="5" customWidth="1"/>
+    <col min="20" max="20" width="18.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -4065,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4089,7 +4092,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1">
@@ -4142,16 +4145,16 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -4204,16 +4207,16 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -4254,19 +4257,19 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>28</v>
@@ -4275,12 +4278,12 @@
         <v>28</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -4342,55 +4345,55 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T6" s="5"/>
     </row>
     <row r="7" spans="1:20" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4422,16 +4425,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -4458,10 +4461,10 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
@@ -4475,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4499,7 +4502,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -4552,10 +4555,10 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -4608,10 +4611,10 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -4652,16 +4655,16 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>29</v>
@@ -4672,7 +4675,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -4728,53 +4731,53 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4804,16 +4807,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
@@ -4832,15 +4835,15 @@
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="7" width="12.7109375" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="19.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="5" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" style="5" customWidth="1"/>
-    <col min="16" max="16" width="18.7109375" style="5" customWidth="1"/>
-    <col min="17" max="18" width="17.7109375" style="5" customWidth="1"/>
+    <col min="16" max="17" width="18.7109375" style="5" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" style="5" customWidth="1"/>
     <col min="19" max="19" width="12.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4849,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4873,7 +4876,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -4926,13 +4929,13 @@
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -4985,13 +4988,13 @@
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -5032,19 +5035,19 @@
         <v>33</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>29</v>
@@ -5055,7 +5058,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -5114,54 +5117,54 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -5192,16 +5195,16 @@
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
-      <formula1>"AA,Shared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="P8:P1007">
